--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513664_FASEFINALBFFB3_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513664_FASEFINALBFFB3_PROCESSED.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.6783</v>
+        <v>6.5704</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0703</v>
+        <v>4.3241</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6081</v>
+        <v>2.2463</v>
       </c>
       <c r="G2" t="n">
         <v>3.1604</v>
@@ -610,13 +610,13 @@
         <v>2.3368</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4759</v>
+        <v>0.368</v>
       </c>
       <c r="T2" t="n">
-        <v>2.8214</v>
+        <v>1.0752</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3455</v>
+        <v>-0.7072000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>3.6262</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. DIAZ ROLLANO</t>
+          <t>R. REID</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5941</v>
+        <v>3.7562</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3351</v>
+        <v>1.4138</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2589</v>
+        <v>2.3425</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0471</v>
+        <v>0.496</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8349</v>
+        <v>1.5753</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2122</v>
+        <v>-1.0793</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2442</v>
+        <v>-1.0069</v>
       </c>
       <c r="K3" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.3054</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1621</v>
+        <v>-1.3123</v>
       </c>
       <c r="M3" t="n">
-        <v>2.8029</v>
+        <v>1.5029</v>
       </c>
       <c r="N3" t="n">
-        <v>1.7528</v>
+        <v>1.2699</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0501</v>
+        <v>0.233</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1684</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.921</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1684</v>
+        <v>2.1421</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3351</v>
+        <v>-1.4702</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1301</v>
+        <v>-0.1015</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.205</v>
+        <v>-1.3687</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7137</v>
+        <v>5.5094</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2211</v>
+        <v>5.4432</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5074</v>
+        <v>0.06619999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. REID</t>
+          <t>A. DIAZ ROLLANO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9734</v>
+        <v>3.6057</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8535</v>
+        <v>1.2355</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1199</v>
+        <v>2.3702</v>
       </c>
       <c r="G4" t="n">
-        <v>0.496</v>
+        <v>3.0471</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5753</v>
+        <v>1.8349</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.0793</v>
+        <v>1.2122</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.0069</v>
+        <v>0.2442</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3054</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.3123</v>
+        <v>0.1621</v>
       </c>
       <c r="M4" t="n">
-        <v>1.5029</v>
+        <v>2.8029</v>
       </c>
       <c r="N4" t="n">
-        <v>1.2699</v>
+        <v>1.7528</v>
       </c>
       <c r="O4" t="n">
-        <v>0.233</v>
+        <v>1.0501</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7789</v>
+        <v>1.1684</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.921</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1421</v>
+        <v>1.1684</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.253</v>
+        <v>-1.3235</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6617</v>
+        <v>-0.2298</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.5913</v>
+        <v>-1.0937</v>
       </c>
       <c r="V4" t="n">
-        <v>5.5094</v>
+        <v>0.7137</v>
       </c>
       <c r="W4" t="n">
-        <v>5.4432</v>
+        <v>1.2211</v>
       </c>
       <c r="X4" t="n">
-        <v>0.06619999999999999</v>
+        <v>-0.5074</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. EDOKPAYI MANCERA</t>
+          <t>A. ARTILES AGUILAR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6325</v>
+        <v>3.4131</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7379</v>
+        <v>1.767</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8945</v>
+        <v>1.646</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1761</v>
+        <v>-0.7632</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4024</v>
+        <v>-1.2239</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7737</v>
+        <v>0.4607</v>
       </c>
       <c r="J5" t="n">
-        <v>4.0627</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.326</v>
+        <v>-1.8293</v>
       </c>
       <c r="L5" t="n">
-        <v>3.7368</v>
+        <v>1.1515</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1133</v>
+        <v>-0.0854</v>
       </c>
       <c r="N5" t="n">
-        <v>1.0765</v>
+        <v>0.6054</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9631</v>
+        <v>-0.6907</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5842000000000001</v>
+        <v>2.1421</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9474</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5316</v>
+        <v>2.1421</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6273</v>
+        <v>-0.4079</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3775</v>
+        <v>0.0028</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2499</v>
+        <v>-0.4107</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.5005</v>
+        <v>2.4421</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.4421</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.5005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ARTILES AGUILAR</t>
+          <t>B. EDOKPAYI MANCERA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2075</v>
+        <v>2.9222</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7841</v>
+        <v>2.2225</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4234</v>
+        <v>0.6997</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7632</v>
+        <v>4.1761</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2239</v>
+        <v>1.4024</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4607</v>
+        <v>2.7737</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6778999999999999</v>
+        <v>4.0627</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.8293</v>
+        <v>0.326</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1515</v>
+        <v>3.7368</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0854</v>
+        <v>0.1133</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6054</v>
+        <v>1.0765</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6907</v>
+        <v>-0.9631</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1421</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1421</v>
+        <v>2.5316</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.6135</v>
+        <v>-0.3376</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9801</v>
+        <v>0.1071</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6333</v>
+        <v>-0.4446</v>
       </c>
       <c r="V6" t="n">
-        <v>2.4421</v>
+        <v>-1.5005</v>
       </c>
       <c r="W6" t="n">
-        <v>2.4421</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. SANCHES CARDOSO MENDES</t>
+          <t>B. GARCIA ALVAREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0132</v>
+        <v>1.2889</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5236</v>
+        <v>0.7843</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5368</v>
+        <v>0.5046</v>
       </c>
       <c r="G7" t="n">
-        <v>1.379</v>
+        <v>-1.2515</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4136</v>
+        <v>0.509</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7927</v>
+        <v>-1.7605</v>
       </c>
       <c r="J7" t="n">
-        <v>0.08550000000000001</v>
+        <v>-1.2674</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.644</v>
+        <v>-0.6029</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7295</v>
+        <v>-0.6645</v>
       </c>
       <c r="M7" t="n">
-        <v>1.2935</v>
+        <v>0.0159</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2303</v>
+        <v>1.1119</v>
       </c>
       <c r="O7" t="n">
-        <v>1.0632</v>
+        <v>-1.096</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9737</v>
+        <v>-1.9474</v>
       </c>
       <c r="R7" t="n">
         <v>0.9737</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0864</v>
+        <v>-0.1491</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3646</v>
+        <v>0.336</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.451</v>
+        <v>-0.485</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2795</v>
+        <v>3.6632</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.6632</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9014</v>
+        <v>0.991</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1047</v>
+        <v>-0.0429</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0061</v>
+        <v>1.0339</v>
       </c>
       <c r="G8" t="n">
         <v>1.5809</v>
@@ -1078,13 +1078,13 @@
         <v>0.3895</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1868</v>
+        <v>-1.0971</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2473</v>
+        <v>-0.1855</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9395</v>
+        <v>-0.9116</v>
       </c>
       <c r="V8" t="n">
         <v>0.1178</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MONTENEGRO MOYA</t>
+          <t>R. SANCHES CARDOSO MENDES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5193</v>
+        <v>0.5472</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>-0.8227</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5193</v>
+        <v>1.3698</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2658</v>
+        <v>1.379</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1329</v>
+        <v>-0.4136</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1329</v>
+        <v>1.7927</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0.644</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.7295</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2658</v>
+        <v>1.2935</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1329</v>
+        <v>0.2303</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1329</v>
+        <v>1.0632</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.9737</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2535</v>
+        <v>-0.5524</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.0655</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2535</v>
+        <v>-0.6179</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. GARCIA ALVAREZ</t>
+          <t>A. MONTENEGRO MOYA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4242</v>
+        <v>0.4358</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0866</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3376</v>
+        <v>0.4358</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2515</v>
+        <v>0.2658</v>
       </c>
       <c r="H10" t="n">
-        <v>0.509</v>
+        <v>0.1329</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.7605</v>
+        <v>0.1329</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2674</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6029</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6645</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0159</v>
+        <v>0.2658</v>
       </c>
       <c r="N10" t="n">
-        <v>1.1119</v>
+        <v>0.1329</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.096</v>
+        <v>0.1329</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9474</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9737</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0137</v>
+        <v>0.17</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3618</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.652</v>
+        <v>0.17</v>
       </c>
       <c r="V10" t="n">
-        <v>3.6632</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>3.6632</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. HETOR MENSAH</t>
+          <t>E. EGEA SOLER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0946</v>
+        <v>-2.0842</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0733</v>
+        <v>-1.8031</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0212</v>
+        <v>-0.2811</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.5379</v>
+        <v>-1.7297</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4937</v>
+        <v>-1.2142</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0442</v>
+        <v>-0.5155</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.784</v>
+        <v>-2.1576</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2411</v>
+        <v>-1.5419</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5429</v>
+        <v>-0.6156</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7538</v>
+        <v>0.4279</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2526</v>
+        <v>0.3278</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.5013</v>
+        <v>0.1001</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1947</v>
+        <v>0.7789</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9474</v>
+        <v>-0.9737</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1421</v>
+        <v>1.7526</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1824</v>
+        <v>-1.5307</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6581</v>
+        <v>0.1071</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4757</v>
+        <v>-1.6377</v>
       </c>
       <c r="V11" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.3973</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X11" t="n">
-        <v>0.06619999999999999</v>
+        <v>-0.8238</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. EGEA SOLER</t>
+          <t>M. HETOR MENSAH</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.7975</v>
+        <v>-2.1579</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3495</v>
+        <v>-2.0254</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.448</v>
+        <v>-0.1325</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.7297</v>
+        <v>-2.5379</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2142</v>
+        <v>-0.4937</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5155</v>
+        <v>-2.0442</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.1576</v>
+        <v>-0.784</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.5419</v>
+        <v>-0.2411</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6156</v>
+        <v>-0.5429</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4279</v>
+        <v>-1.7538</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3278</v>
+        <v>-0.2526</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1001</v>
+        <v>-1.5013</v>
       </c>
       <c r="P12" t="n">
-        <v>0.7789</v>
+        <v>0.1947</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9737</v>
+        <v>-1.9474</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7526</v>
+        <v>2.1421</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.244</v>
+        <v>0.1191</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4393</v>
+        <v>0.706</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.8047</v>
+        <v>-0.587</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3973</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2211</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.8238</v>
+        <v>0.06619999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,34 +1423,34 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>18.0518</v>
+        <v>19.2884</v>
       </c>
       <c r="E13" t="n">
-        <v>5.816400000000001</v>
+        <v>7.053099999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>12.2354</v>
+        <v>12.2352</v>
       </c>
       <c r="G13" t="n">
         <v>7.823</v>
       </c>
       <c r="H13" t="n">
-        <v>7.1913</v>
+        <v>7.191299999999998</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6318</v>
+        <v>0.6317999999999997</v>
       </c>
       <c r="J13" t="n">
-        <v>1.913200000000001</v>
+        <v>1.9132</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.9741999999999998</v>
+        <v>-0.9741999999999996</v>
       </c>
       <c r="L13" t="n">
-        <v>2.887799999999999</v>
+        <v>2.8878</v>
       </c>
       <c r="M13" t="n">
-        <v>5.909700000000001</v>
+        <v>5.9097</v>
       </c>
       <c r="N13" t="n">
         <v>8.165700000000001</v>
@@ -1468,13 +1468,13 @@
         <v>16.5526</v>
       </c>
       <c r="S13" t="n">
-        <v>-7.448</v>
+        <v>-6.211399999999998</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6463000000000003</v>
+        <v>1.8829</v>
       </c>
       <c r="U13" t="n">
-        <v>-8.0944</v>
+        <v>-8.094100000000001</v>
       </c>
       <c r="V13" t="n">
         <v>14.7559</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.2564</v>
+        <v>2.9937</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7899</v>
+        <v>2.1951</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4664</v>
+        <v>0.7986</v>
       </c>
       <c r="G14" t="n">
         <v>-0.3503</v>
@@ -1546,13 +1546,13 @@
         <v>1.5579</v>
       </c>
       <c r="S14" t="n">
-        <v>4.7693</v>
+        <v>2.5067</v>
       </c>
       <c r="T14" t="n">
-        <v>3.5911</v>
+        <v>1.9963</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1782</v>
+        <v>0.5104</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3311</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. BEDIA FERRER</t>
+          <t>A. SAEZ CALABUIG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0711</v>
+        <v>1.1831</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4788</v>
+        <v>1.4531</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4077</v>
+        <v>-0.27</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1713</v>
+        <v>3.6472</v>
       </c>
       <c r="H15" t="n">
-        <v>0.231</v>
+        <v>0.6405</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4023</v>
+        <v>3.0067</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5009</v>
+        <v>2.9115</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3388</v>
+        <v>0.2772</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1621</v>
+        <v>2.6342</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6722</v>
+        <v>0.7357</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1078</v>
+        <v>0.3632</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5644</v>
+        <v>0.3725</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1947</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1684</v>
+        <v>-3.3105</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3632</v>
+        <v>1.7526</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2687</v>
+        <v>1.536</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9252</v>
+        <v>1.5727</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3435</v>
+        <v>-0.0367</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2211</v>
+        <v>-2.4421</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2211</v>
+        <v>0.2795</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.4421</v>
+        <v>-2.7216</v>
       </c>
     </row>
     <row r="16">
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. SAEZ CALABUIG</t>
+          <t>M. ALONSO ARNEDO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.534</v>
+        <v>0.2773</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0544</v>
+        <v>-1.1668</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5204</v>
+        <v>1.4441</v>
       </c>
       <c r="G17" t="n">
-        <v>3.6472</v>
+        <v>-0.2474</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6405</v>
+        <v>-0.1955</v>
       </c>
       <c r="I17" t="n">
-        <v>3.0067</v>
+        <v>-0.0518</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9115</v>
+        <v>-1.1659</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2772</v>
+        <v>-0.5824</v>
       </c>
       <c r="L17" t="n">
-        <v>2.6342</v>
+        <v>-0.5835</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7357</v>
+        <v>0.9185</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3632</v>
+        <v>0.3869</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3725</v>
+        <v>0.5316</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.5579</v>
+        <v>0.7789</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.3105</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7526</v>
+        <v>0.7789</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8868</v>
+        <v>-0.2543</v>
       </c>
       <c r="T17" t="n">
-        <v>1.174</v>
+        <v>-0.0009</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2871</v>
+        <v>-0.2533</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.4421</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2795</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.7216</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. GONZALEZ JURADO</t>
+          <t>J. BEDIA FERRER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0886</v>
+        <v>-0.0154</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1782</v>
+        <v>1.482</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2668</v>
+        <v>-1.4974</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7355</v>
+        <v>-0.1713</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1966</v>
+        <v>0.231</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9321</v>
+        <v>-0.4023</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3579</v>
+        <v>0.5009</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0205</v>
+        <v>0.3388</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3374</v>
+        <v>0.1621</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6224</v>
+        <v>-0.6722</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2171</v>
+        <v>-0.1078</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4053</v>
+        <v>-0.5644</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5579</v>
+        <v>0.1947</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9474</v>
+        <v>-1.1684</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3895</v>
+        <v>1.3632</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4543</v>
+        <v>1.1823</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4882</v>
+        <v>0.9285</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.034</v>
+        <v>0.2538</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2795</v>
+        <v>-1.2211</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2795</v>
+        <v>1.2211</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. ALONSO ARNEDO</t>
+          <t>O. GONZALEZ JURADO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3216</v>
+        <v>-0.332</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4658</v>
+        <v>-0.1208</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1442</v>
+        <v>-0.2112</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2474</v>
+        <v>0.7355</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1955</v>
+        <v>-0.1966</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0518</v>
+        <v>0.9321</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.1659</v>
+        <v>1.3579</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5824</v>
+        <v>0.0205</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5835</v>
+        <v>1.3374</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9185</v>
+        <v>-0.6224</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3869</v>
+        <v>-0.2171</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5316</v>
+        <v>-0.4053</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7789</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7789</v>
+        <v>0.3895</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8531</v>
+        <v>0.2109</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2999</v>
+        <v>0.1892</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5532</v>
+        <v>0.0217</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. ISIDRO PENA</t>
+          <t>E. LLACER SIMLAT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2742</v>
+        <v>-0.9431</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0426</v>
+        <v>-1.988</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2316</v>
+        <v>1.0448</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1242</v>
+        <v>1.0602</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2053</v>
+        <v>-1.0991</v>
       </c>
       <c r="I20" t="n">
-        <v>0.08110000000000001</v>
+        <v>2.1592</v>
       </c>
       <c r="J20" t="n">
-        <v>0.08110000000000001</v>
+        <v>1.5258</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>-1.0518</v>
       </c>
       <c r="L20" t="n">
-        <v>0.08110000000000001</v>
+        <v>2.5776</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2053</v>
+        <v>-0.4657</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2053</v>
+        <v>-0.0473</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-0.4184</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1947</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3.3105</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1947</v>
+        <v>2.1421</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1237</v>
+        <v>0.1583</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1237</v>
+        <v>0.5104</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>-0.3521</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2211</v>
+        <v>-0.9932</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.7137</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2211</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. LLACER SIMLAT</t>
+          <t>M. ISIDRO PENA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4491</v>
+        <v>-1.1745</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2837</v>
+        <v>0.0571</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8347</v>
+        <v>-1.2316</v>
       </c>
       <c r="G21" t="n">
-        <v>1.0602</v>
+        <v>-0.1242</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0991</v>
+        <v>-0.2053</v>
       </c>
       <c r="I21" t="n">
-        <v>2.1592</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>1.5258</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.0518</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>2.5776</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4657</v>
+        <v>-0.2053</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0473</v>
+        <v>-0.2053</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4184</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.1684</v>
+        <v>0.1947</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.3105</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1421</v>
+        <v>0.1947</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3477</v>
+        <v>-0.024</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7854</v>
+        <v>-0.024</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5623</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9932</v>
+        <v>-1.2211</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.7137</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2795</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. TERRADES DAROQUI</t>
+          <t>J. MERENCIO MORENO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8744</v>
+        <v>-1.6853</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.83</v>
+        <v>-1.7209</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0443</v>
+        <v>0.0356</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7365</v>
+        <v>-2.3306</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.3217</v>
+        <v>-1.3126</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5853</v>
+        <v>-1.0179</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0577</v>
+        <v>-2.565</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.3468</v>
+        <v>-1.447</v>
       </c>
       <c r="L22" t="n">
-        <v>1.2891</v>
+        <v>-1.118</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6788</v>
+        <v>0.2344</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0251</v>
+        <v>0.1343</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7039</v>
+        <v>0.1001</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5842000000000001</v>
+        <v>2.1421</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9474</v>
+        <v>-0.3895</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3632</v>
+        <v>2.5316</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2779</v>
+        <v>0.6142</v>
       </c>
       <c r="T22" t="n">
-        <v>0.8371</v>
+        <v>0.623</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5592</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.8316</v>
+        <v>-2.1111</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6621</v>
+        <v>0.6105</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1695</v>
+        <v>-2.7216</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1704</v>
+        <v>-2.5777</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0273</v>
+        <v>-2.7283</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1431</v>
+        <v>0.1506</v>
       </c>
       <c r="G23" t="n">
         <v>-0.8028999999999999</v>
@@ -2248,13 +2248,13 @@
         <v>0.7789</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3617</v>
+        <v>0.231</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2538</v>
+        <v>0.0452</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1079</v>
+        <v>0.1857</v>
       </c>
       <c r="V23" t="n">
         <v>0.3311</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. MERENCIO MORENO</t>
+          <t>A. TERRADES DAROQUI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2145</v>
+        <v>-2.8009</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8174</v>
+        <v>-2.3284</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3971</v>
+        <v>-0.4725</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.3306</v>
+        <v>-0.7365</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.3126</v>
+        <v>-1.3217</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.0179</v>
+        <v>0.5853</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.565</v>
+        <v>-0.0577</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.447</v>
+        <v>-1.3468</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.118</v>
+        <v>1.2891</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2344</v>
+        <v>-0.6788</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1343</v>
+        <v>0.0251</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1001</v>
+        <v>-0.7039</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1421</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.3895</v>
+        <v>-1.9474</v>
       </c>
       <c r="R24" t="n">
-        <v>2.5316</v>
+        <v>1.3632</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.915</v>
+        <v>0.3514</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4734</v>
+        <v>0.3387</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4415</v>
+        <v>0.0127</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.1111</v>
+        <v>-1.8316</v>
       </c>
       <c r="W24" t="n">
-        <v>0.6105</v>
+        <v>-0.6621</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.7216</v>
+        <v>-1.1695</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>F. GOMEZ CARBONELL</t>
+          <t>D. CALERO BAUTISTA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.6165</v>
+        <v>-6.125</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.4169</v>
+        <v>-4.9626</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.1996</v>
+        <v>-1.1624</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.9246</v>
+        <v>-6.1861</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1611</v>
+        <v>-2.8504</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.7635</v>
+        <v>-3.3357</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.8997</v>
+        <v>-5.9677</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.2822</v>
+        <v>-3.3097</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.6175</v>
+        <v>-2.658</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0249</v>
+        <v>-0.2184</v>
       </c>
       <c r="N25" t="n">
-        <v>0.1211</v>
+        <v>0.4592</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.146</v>
+        <v>-0.6776</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.5842000000000001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0.3895</v>
       </c>
       <c r="S25" t="n">
-        <v>1.6071</v>
+        <v>1.1721</v>
       </c>
       <c r="T25" t="n">
-        <v>1.5081</v>
+        <v>1.0051</v>
       </c>
       <c r="U25" t="n">
-        <v>0.099</v>
+        <v>0.167</v>
       </c>
       <c r="V25" t="n">
-        <v>-3.7147</v>
+        <v>-1.5005</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.0516</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-3.6632</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>D. CALERO BAUTISTA</t>
+          <t>F. GOMEZ CARBONELL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.5121</v>
+        <v>-6.131</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.461</v>
+        <v>-3.0149</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.0511</v>
+        <v>-3.1161</v>
       </c>
       <c r="G26" t="n">
-        <v>-6.1861</v>
+        <v>-2.9246</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.8504</v>
+        <v>-0.1611</v>
       </c>
       <c r="I26" t="n">
-        <v>-3.3357</v>
+        <v>-2.7635</v>
       </c>
       <c r="J26" t="n">
-        <v>-5.9677</v>
+        <v>-2.8997</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.3097</v>
+        <v>-0.2822</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.658</v>
+        <v>-2.6175</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.2184</v>
+        <v>-0.0249</v>
       </c>
       <c r="N26" t="n">
-        <v>0.4592</v>
+        <v>0.1211</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.6776</v>
+        <v>-0.146</v>
       </c>
       <c r="P26" t="n">
-        <v>0.3895</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R26" t="n">
         <v>0.3895</v>
       </c>
       <c r="S26" t="n">
-        <v>0.785</v>
+        <v>1.0925</v>
       </c>
       <c r="T26" t="n">
-        <v>0.5067</v>
+        <v>0.91</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2783</v>
+        <v>0.1825</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.5005</v>
+        <v>-3.7147</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>-0.0516</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.5005</v>
+        <v>-3.6632</v>
       </c>
     </row>
     <row r="27">
@@ -2515,25 +2515,25 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-18.052</v>
+        <v>-16.7229</v>
       </c>
       <c r="E27" t="n">
         <v>-12.2355</v>
       </c>
       <c r="F27" t="n">
-        <v>-5.8164</v>
+        <v>-4.487500000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>-7.8231</v>
+        <v>-7.823099999999998</v>
       </c>
       <c r="H27" t="n">
-        <v>-7.1913</v>
+        <v>-7.191300000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.6316000000000002</v>
+        <v>-0.6315999999999993</v>
       </c>
       <c r="J27" t="n">
-        <v>-5.909799999999999</v>
+        <v>-5.9098</v>
       </c>
       <c r="K27" t="n">
         <v>-8.165799999999999</v>
@@ -2545,7 +2545,7 @@
         <v>-1.9134</v>
       </c>
       <c r="N27" t="n">
-        <v>0.9742</v>
+        <v>0.9742000000000002</v>
       </c>
       <c r="O27" t="n">
         <v>-2.8876</v>
@@ -2560,13 +2560,13 @@
         <v>13.6316</v>
       </c>
       <c r="S27" t="n">
-        <v>7.447900000000001</v>
+        <v>8.777099999999999</v>
       </c>
       <c r="T27" t="n">
         <v>8.094200000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.6462000000000003</v>
+        <v>0.6829</v>
       </c>
       <c r="V27" t="n">
         <v>-14.7559</v>
